--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_SANDA ELECTROCLIMA TECLA SALA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_SANDA ELECTROCLIMA TECLA SALA.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V. MANDIM SILVA</t>
+          <t>E. MARTÍN GASCÓN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,70 +562,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>8.372400000000001</v>
+        <v>7.507000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>-4.245800000000001</v>
+        <v>-1.6975</v>
       </c>
       <c r="F2" t="n">
-        <v>12.618</v>
+        <v>9.2049</v>
       </c>
       <c r="G2" t="n">
-        <v>13.6116</v>
+        <v>-20.5851</v>
       </c>
       <c r="H2" t="n">
-        <v>16.2974</v>
+        <v>-14.3878</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.685300000000001</v>
+        <v>-6.1972</v>
       </c>
       <c r="J2" t="n">
-        <v>39.3062</v>
+        <v>13.8273</v>
       </c>
       <c r="K2" t="n">
-        <v>33.2074</v>
+        <v>8.272500000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>6.0987</v>
+        <v>5.5548</v>
       </c>
       <c r="M2" t="n">
-        <v>-25.6943</v>
+        <v>-34.4123</v>
       </c>
       <c r="N2" t="n">
-        <v>-16.9103</v>
+        <v>-22.6602</v>
       </c>
       <c r="O2" t="n">
-        <v>-8.784000000000001</v>
+        <v>-11.7522</v>
       </c>
       <c r="P2" t="n">
-        <v>-4.883599999999999</v>
+        <v>14.4556</v>
       </c>
       <c r="Q2" t="n">
-        <v>-48.8356</v>
+        <v>-32.4268</v>
       </c>
       <c r="R2" t="n">
-        <v>43.952</v>
+        <v>46.8826</v>
       </c>
       <c r="S2" t="n">
-        <v>4.1975</v>
+        <v>-3.118</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6805999999999998</v>
+        <v>-1.6607</v>
       </c>
       <c r="U2" t="n">
-        <v>3.5171</v>
+        <v>-1.4574</v>
       </c>
       <c r="V2" t="n">
-        <v>-4.553699999999999</v>
+        <v>16.7548</v>
       </c>
       <c r="W2" t="n">
-        <v>4.6031</v>
+        <v>18.5625</v>
       </c>
       <c r="X2" t="n">
-        <v>-9.156499999999999</v>
+        <v>-1.8076</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0385</v>
+        <v>3.620899999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>10.3167</v>
+        <v>7.099399999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>-7.2782</v>
+        <v>-3.478999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>-20.9071</v>
@@ -688,13 +688,13 @@
         <v>50.5939</v>
       </c>
       <c r="S3" t="n">
-        <v>-3.1245</v>
+        <v>-2.5422</v>
       </c>
       <c r="T3" t="n">
-        <v>3.7737</v>
+        <v>0.5564</v>
       </c>
       <c r="U3" t="n">
-        <v>-6.8982</v>
+        <v>-3.0986</v>
       </c>
       <c r="V3" t="n">
         <v>22.7729</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. MARTÍN GASCÓN</t>
+          <t>V. MANDIM SILVA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>2.885900000000002</v>
+        <v>2.6291</v>
       </c>
       <c r="E4" t="n">
-        <v>-6.5488</v>
+        <v>-7.463000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>9.434999999999999</v>
+        <v>10.0923</v>
       </c>
       <c r="G4" t="n">
-        <v>-20.5851</v>
+        <v>13.6116</v>
       </c>
       <c r="H4" t="n">
-        <v>-14.3878</v>
+        <v>16.2974</v>
       </c>
       <c r="I4" t="n">
-        <v>-6.1972</v>
+        <v>-2.685300000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>13.8273</v>
+        <v>39.3062</v>
       </c>
       <c r="K4" t="n">
-        <v>8.272500000000001</v>
+        <v>33.2074</v>
       </c>
       <c r="L4" t="n">
-        <v>5.5548</v>
+        <v>6.0987</v>
       </c>
       <c r="M4" t="n">
-        <v>-34.4123</v>
+        <v>-25.6943</v>
       </c>
       <c r="N4" t="n">
-        <v>-22.6602</v>
+        <v>-16.9103</v>
       </c>
       <c r="O4" t="n">
-        <v>-11.7522</v>
+        <v>-8.784000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>14.4556</v>
+        <v>-4.883599999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>-32.4268</v>
+        <v>-48.8356</v>
       </c>
       <c r="R4" t="n">
-        <v>46.8826</v>
+        <v>43.952</v>
       </c>
       <c r="S4" t="n">
-        <v>-7.739299999999999</v>
+        <v>-1.5457</v>
       </c>
       <c r="T4" t="n">
-        <v>-6.5117</v>
+        <v>-2.5369</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.2277</v>
+        <v>0.9912999999999997</v>
       </c>
       <c r="V4" t="n">
-        <v>16.7548</v>
+        <v>-4.553699999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>18.5625</v>
+        <v>4.6031</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.8076</v>
+        <v>-9.156499999999999</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.003399999999999</v>
+        <v>1.187599999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.820600000000002</v>
+        <v>-1.052100000000002</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8173</v>
+        <v>2.2395</v>
       </c>
       <c r="G5" t="n">
         <v>-11.9665</v>
@@ -844,13 +844,13 @@
         <v>43.3661</v>
       </c>
       <c r="S5" t="n">
-        <v>-3.1625</v>
+        <v>0.02830000000000032</v>
       </c>
       <c r="T5" t="n">
-        <v>-2.850099999999999</v>
+        <v>-0.08150000000000004</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3127000000000002</v>
+        <v>0.1093</v>
       </c>
       <c r="V5" t="n">
         <v>4.139800000000001</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.0053</v>
+        <v>-1.9042</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1141</v>
+        <v>-0.013</v>
       </c>
       <c r="F6" t="n">
         <v>-1.8912</v>
@@ -922,10 +922,10 @@
         <v>0.586</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0605</v>
+        <v>0.1616</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2421</v>
+        <v>-0.141</v>
       </c>
       <c r="U6" t="n">
         <v>0.3026</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. GARCIA LOPEZ</t>
+          <t>M. TOLEDO CIVICO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.7789</v>
+        <v>-3.3118</v>
       </c>
       <c r="E7" t="n">
-        <v>5.3239</v>
+        <v>-3.7435</v>
       </c>
       <c r="F7" t="n">
-        <v>-8.1029</v>
+        <v>0.4316999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>5.889900000000001</v>
+        <v>0.7488999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>3.782899999999999</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1071</v>
+        <v>0.1879000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>29.0996</v>
+        <v>0.365</v>
       </c>
       <c r="K7" t="n">
-        <v>18.21</v>
+        <v>0.3107</v>
       </c>
       <c r="L7" t="n">
-        <v>10.8892</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-23.2097</v>
+        <v>0.3838</v>
       </c>
       <c r="N7" t="n">
-        <v>-14.4271</v>
+        <v>0.2502</v>
       </c>
       <c r="O7" t="n">
-        <v>-8.782299999999999</v>
+        <v>0.1336000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>3.5162</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q7" t="n">
-        <v>-33.4033</v>
+        <v>-2.9301</v>
       </c>
       <c r="R7" t="n">
-        <v>36.9199</v>
+        <v>1.758</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3824999999999998</v>
+        <v>-1.3929</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0947</v>
+        <v>-0.7914</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7123999999999999</v>
+        <v>-0.6013999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>-12.5675</v>
+        <v>-1.4958</v>
       </c>
       <c r="W7" t="n">
-        <v>8.533299999999999</v>
+        <v>-0.387</v>
       </c>
       <c r="X7" t="n">
-        <v>-21.1009</v>
+        <v>-1.1089</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. TOLEDO CIVICO</t>
+          <t>M. GARCIA LOPEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.588</v>
+        <v>-3.9831</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.6423</v>
+        <v>5.301999999999998</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05449999999999999</v>
+        <v>-9.2851</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7488999999999999</v>
+        <v>5.889900000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5610000000000001</v>
+        <v>3.782899999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1879000000000001</v>
+        <v>2.1071</v>
       </c>
       <c r="J8" t="n">
-        <v>0.365</v>
+        <v>29.0996</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3107</v>
+        <v>18.21</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05430000000000001</v>
+        <v>10.8892</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3838</v>
+        <v>-23.2097</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2502</v>
+        <v>-14.4271</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1336000000000001</v>
+        <v>-8.782299999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1721</v>
+        <v>3.5162</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9301</v>
+        <v>-33.4033</v>
       </c>
       <c r="R8" t="n">
-        <v>1.758</v>
+        <v>36.9199</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.6689</v>
+        <v>-0.8215999999999998</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6902999999999999</v>
+        <v>1.0728</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9785999999999999</v>
+        <v>-1.8943</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.4958</v>
+        <v>-12.5675</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.387</v>
+        <v>8.533299999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1089</v>
+        <v>-21.1009</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.5748</v>
+        <v>-4.4723</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.7785</v>
+        <v>-5.0819</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2038</v>
+        <v>0.6095</v>
       </c>
       <c r="G9" t="n">
         <v>-5.7207</v>
@@ -1156,13 +1156,13 @@
         <v>3.1254</v>
       </c>
       <c r="S9" t="n">
-        <v>1.5132</v>
+        <v>1.6157</v>
       </c>
       <c r="T9" t="n">
-        <v>1.8766</v>
+        <v>1.5733</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3634000000000001</v>
+        <v>0.04249999999999998</v>
       </c>
       <c r="V9" t="n">
         <v>0.6093</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. FERRARI</t>
+          <t>J. BERTOMEU BALDÉ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.6256</v>
+        <v>-4.9444</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4568000000000003</v>
+        <v>-5.503</v>
       </c>
       <c r="F10" t="n">
-        <v>-7.1687</v>
+        <v>0.5588000000000006</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.7604</v>
+        <v>7.445399999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.4612</v>
+        <v>7.016</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7009</v>
+        <v>0.4294000000000008</v>
       </c>
       <c r="J10" t="n">
-        <v>3.2477</v>
+        <v>15.2027</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0053</v>
+        <v>13.2822</v>
       </c>
       <c r="L10" t="n">
-        <v>2.2424</v>
+        <v>1.9207</v>
       </c>
       <c r="M10" t="n">
-        <v>-5.008</v>
+        <v>-7.7573</v>
       </c>
       <c r="N10" t="n">
-        <v>-4.4666</v>
+        <v>-6.266</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5414999999999999</v>
+        <v>-1.4912</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1953</v>
+        <v>-6.0558</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.344</v>
+        <v>-22.6597</v>
       </c>
       <c r="R10" t="n">
-        <v>2.5393</v>
+        <v>16.6039</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.371</v>
+        <v>-1.216</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.9697</v>
+        <v>-1.2053</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4011</v>
+        <v>-0.01069999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.6894</v>
+        <v>-5.1183</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6093</v>
+        <v>3.1592</v>
       </c>
       <c r="X10" t="n">
-        <v>-4.2987</v>
+        <v>-8.2775</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. GONZÁLEZ BRUMOS</t>
+          <t>G. FERRARI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.540199999999999</v>
+        <v>-5.016499999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-10.5246</v>
+        <v>1.2821</v>
       </c>
       <c r="F11" t="n">
-        <v>1.9844</v>
+        <v>-6.2984</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.0645</v>
+        <v>-1.7604</v>
       </c>
       <c r="H11" t="n">
-        <v>-5.3283</v>
+        <v>-3.4612</v>
       </c>
       <c r="I11" t="n">
-        <v>3.264</v>
+        <v>1.7009</v>
       </c>
       <c r="J11" t="n">
-        <v>9.524900000000001</v>
+        <v>3.2477</v>
       </c>
       <c r="K11" t="n">
-        <v>3.4227</v>
+        <v>1.0053</v>
       </c>
       <c r="L11" t="n">
-        <v>6.102399999999999</v>
+        <v>2.2424</v>
       </c>
       <c r="M11" t="n">
-        <v>-11.5895</v>
+        <v>-5.008</v>
       </c>
       <c r="N11" t="n">
-        <v>-8.751099999999999</v>
+        <v>-4.4666</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.8384</v>
+        <v>-0.5414999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.9301</v>
+        <v>0.1953</v>
       </c>
       <c r="Q11" t="n">
-        <v>-23.0506</v>
+        <v>-2.344</v>
       </c>
       <c r="R11" t="n">
-        <v>20.1205</v>
+        <v>2.5393</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2236</v>
+        <v>0.238</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.435</v>
+        <v>-0.2309</v>
       </c>
       <c r="U11" t="n">
-        <v>1.2116</v>
+        <v>0.4689</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.322</v>
+        <v>-3.6894</v>
       </c>
       <c r="W11" t="n">
-        <v>4.435700000000001</v>
+        <v>0.6093</v>
       </c>
       <c r="X11" t="n">
-        <v>-7.7577</v>
+        <v>-4.2987</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. BERTOMEU BALDÉ</t>
+          <t>P. GONZÁLEZ BRUMOS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.909800000000001</v>
+        <v>-8.0898</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.9695</v>
+        <v>-9.473700000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9402</v>
+        <v>1.3839</v>
       </c>
       <c r="G12" t="n">
-        <v>7.445399999999999</v>
+        <v>-2.0645</v>
       </c>
       <c r="H12" t="n">
-        <v>7.016</v>
+        <v>-5.3283</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4294000000000008</v>
+        <v>3.264</v>
       </c>
       <c r="J12" t="n">
-        <v>15.2027</v>
+        <v>9.524900000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>13.2822</v>
+        <v>3.4227</v>
       </c>
       <c r="L12" t="n">
-        <v>1.9207</v>
+        <v>6.102399999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-7.7573</v>
+        <v>-11.5895</v>
       </c>
       <c r="N12" t="n">
-        <v>-6.266</v>
+        <v>-8.751099999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.4912</v>
+        <v>-2.8384</v>
       </c>
       <c r="P12" t="n">
-        <v>-6.0558</v>
+        <v>-2.9301</v>
       </c>
       <c r="Q12" t="n">
-        <v>-22.6597</v>
+        <v>-23.0506</v>
       </c>
       <c r="R12" t="n">
-        <v>16.6039</v>
+        <v>20.1205</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.1816</v>
+        <v>0.2269000000000002</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.6719</v>
+        <v>-0.3840000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.5096</v>
+        <v>0.6108999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-5.1183</v>
+        <v>-3.322</v>
       </c>
       <c r="W12" t="n">
-        <v>3.1592</v>
+        <v>4.435700000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>-8.2775</v>
+        <v>-7.7577</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>17</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.932</v>
+        <v>-8.308400000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-13.8038</v>
+        <v>-13.6426</v>
       </c>
       <c r="F13" t="n">
-        <v>3.8716</v>
+        <v>5.334300000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-14.7934</v>
@@ -1468,13 +1468,13 @@
         <v>25.5897</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.6221</v>
+        <v>-1.9986</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.3571</v>
+        <v>-1.1966</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.2649</v>
+        <v>-0.8021000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-1.0882</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E. TURNQUEST</t>
+          <t>G. LOZANO MASSANET</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>-13.4317</v>
+        <v>-11.3134</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.9617</v>
+        <v>-15.9396</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.470000000000001</v>
+        <v>4.6262</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.0454</v>
+        <v>-12.0643</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.9048</v>
+        <v>-14.5124</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8596</v>
+        <v>2.448</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1346999999999998</v>
+        <v>-4.4374</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.9406</v>
+        <v>-3.654500000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>2.8059</v>
+        <v>-0.7824999999999998</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.9107</v>
+        <v>-7.627</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.9641</v>
+        <v>-10.8577</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9465999999999999</v>
+        <v>3.2307</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.1488</v>
+        <v>5.665</v>
       </c>
       <c r="Q14" t="n">
-        <v>-6.0556</v>
+        <v>-12.5019</v>
       </c>
       <c r="R14" t="n">
-        <v>3.9067</v>
+        <v>18.1667</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8</v>
+        <v>-6.8968</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2287</v>
+        <v>-2.8236</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.0286</v>
+        <v>-4.0729</v>
       </c>
       <c r="V14" t="n">
-        <v>-6.4374</v>
+        <v>1.9828</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.8234</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.4374</v>
+        <v>-1.8406</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. DALET CASALPRIM</t>
+          <t>E. TURNQUEST</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>-17.3555</v>
+        <v>-12.5614</v>
       </c>
       <c r="E15" t="n">
-        <v>-14.1135</v>
+        <v>-6.366</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.242</v>
+        <v>-6.1952</v>
       </c>
       <c r="G15" t="n">
-        <v>-10.5812</v>
+        <v>-4.0454</v>
       </c>
       <c r="H15" t="n">
-        <v>-10.2313</v>
+        <v>-5.9048</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3496000000000001</v>
+        <v>1.8596</v>
       </c>
       <c r="J15" t="n">
-        <v>7.766399999999999</v>
+        <v>-0.1346999999999998</v>
       </c>
       <c r="K15" t="n">
-        <v>5.2694</v>
+        <v>-2.9406</v>
       </c>
       <c r="L15" t="n">
-        <v>2.497</v>
+        <v>2.8059</v>
       </c>
       <c r="M15" t="n">
-        <v>-18.3476</v>
+        <v>-3.9107</v>
       </c>
       <c r="N15" t="n">
-        <v>-15.501</v>
+        <v>-2.9641</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.8467</v>
+        <v>-0.9465999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>-7.6183</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q15" t="n">
-        <v>-37.1149</v>
+        <v>-6.0556</v>
       </c>
       <c r="R15" t="n">
-        <v>29.4967</v>
+        <v>3.9067</v>
       </c>
       <c r="S15" t="n">
-        <v>15.6145</v>
+        <v>0.07010000000000002</v>
       </c>
       <c r="T15" t="n">
-        <v>13.1241</v>
+        <v>-0.1757000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>2.4906</v>
+        <v>0.246</v>
       </c>
       <c r="V15" t="n">
-        <v>-14.7703</v>
+        <v>-6.4374</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1108</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-16.8814</v>
+        <v>-6.4374</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. LOZANO MASSANET</t>
+          <t>P. MARTÍNEZ SERRANO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>-17.7608</v>
+        <v>-17.0177</v>
       </c>
       <c r="E16" t="n">
-        <v>-19.7208</v>
+        <v>-12.5823</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9599</v>
+        <v>-4.4353</v>
       </c>
       <c r="G16" t="n">
-        <v>-12.0643</v>
+        <v>-12.0378</v>
       </c>
       <c r="H16" t="n">
-        <v>-14.5124</v>
+        <v>-5.6724</v>
       </c>
       <c r="I16" t="n">
-        <v>2.448</v>
+        <v>-6.3654</v>
       </c>
       <c r="J16" t="n">
-        <v>-4.4374</v>
+        <v>-6.366</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.654500000000001</v>
+        <v>-0.003900000000000015</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.7824999999999998</v>
+        <v>-6.362</v>
       </c>
       <c r="M16" t="n">
-        <v>-7.627</v>
+        <v>-5.6719</v>
       </c>
       <c r="N16" t="n">
-        <v>-10.8577</v>
+        <v>-5.668200000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2307</v>
+        <v>-0.003500000000000059</v>
       </c>
       <c r="P16" t="n">
-        <v>5.665</v>
+        <v>-5.0789</v>
       </c>
       <c r="Q16" t="n">
-        <v>-12.5019</v>
+        <v>-11.7206</v>
       </c>
       <c r="R16" t="n">
-        <v>18.1667</v>
+        <v>6.6415</v>
       </c>
       <c r="S16" t="n">
-        <v>-13.3442</v>
+        <v>-0.2331</v>
       </c>
       <c r="T16" t="n">
-        <v>-6.605</v>
+        <v>0.4623</v>
       </c>
       <c r="U16" t="n">
-        <v>-6.7395</v>
+        <v>-0.6953999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>1.9828</v>
+        <v>0.3320000000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>3.8234</v>
+        <v>5.0421</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.8406</v>
+        <v>-4.71</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ SERRANO</t>
+          <t>R. DALET CASALPRIM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D17" t="n">
-        <v>-19.2855</v>
+        <v>-24.9843</v>
       </c>
       <c r="E17" t="n">
-        <v>-13.8968</v>
+        <v>-21.5162</v>
       </c>
       <c r="F17" t="n">
-        <v>-5.388500000000001</v>
+        <v>-3.468000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>-12.0378</v>
+        <v>-10.5812</v>
       </c>
       <c r="H17" t="n">
-        <v>-5.6724</v>
+        <v>-10.2313</v>
       </c>
       <c r="I17" t="n">
-        <v>-6.3654</v>
+        <v>-0.3496000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>-6.366</v>
+        <v>7.766399999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.003900000000000015</v>
+        <v>5.2694</v>
       </c>
       <c r="L17" t="n">
-        <v>-6.362</v>
+        <v>2.497</v>
       </c>
       <c r="M17" t="n">
-        <v>-5.6719</v>
+        <v>-18.3476</v>
       </c>
       <c r="N17" t="n">
-        <v>-5.668200000000001</v>
+        <v>-15.501</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.003500000000000059</v>
+        <v>-2.8467</v>
       </c>
       <c r="P17" t="n">
-        <v>-5.0789</v>
+        <v>-7.6183</v>
       </c>
       <c r="Q17" t="n">
-        <v>-11.7206</v>
+        <v>-37.1149</v>
       </c>
       <c r="R17" t="n">
-        <v>6.6415</v>
+        <v>29.4967</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.5008</v>
+        <v>7.9855</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8522000000000001</v>
+        <v>5.721</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.6484</v>
+        <v>2.2647</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3320000000000001</v>
+        <v>-14.7703</v>
       </c>
       <c r="W17" t="n">
-        <v>5.0421</v>
+        <v>2.1108</v>
       </c>
       <c r="X17" t="n">
-        <v>-4.71</v>
+        <v>-16.8814</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>25</v>
       </c>
       <c r="D18" t="n">
-        <v>-21.6509</v>
+        <v>-25.4836</v>
       </c>
       <c r="E18" t="n">
-        <v>-26.9399</v>
+        <v>-32.0975</v>
       </c>
       <c r="F18" t="n">
-        <v>5.288799999999999</v>
+        <v>6.6137</v>
       </c>
       <c r="G18" t="n">
         <v>-6.9168</v>
@@ -1858,13 +1858,13 @@
         <v>40.0453</v>
       </c>
       <c r="S18" t="n">
-        <v>6.263500000000001</v>
+        <v>2.4311</v>
       </c>
       <c r="T18" t="n">
-        <v>8.0097</v>
+        <v>2.852</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.746</v>
+        <v>-0.4211000000000002</v>
       </c>
       <c r="V18" t="n">
         <v>-12.2071</v>
@@ -1891,13 +1891,13 @@
         <v>25</v>
       </c>
       <c r="D19" t="n">
-        <v>-69.1392</v>
+        <v>-58.3961</v>
       </c>
       <c r="E19" t="n">
-        <v>-60.0809</v>
+        <v>-51.5292</v>
       </c>
       <c r="F19" t="n">
-        <v>-9.058299999999999</v>
+        <v>-6.867399999999999</v>
       </c>
       <c r="G19" t="n">
         <v>-41.9862</v>
@@ -1936,13 +1936,13 @@
         <v>48.2498</v>
       </c>
       <c r="S19" t="n">
-        <v>-16.8312</v>
+        <v>-6.0882</v>
       </c>
       <c r="T19" t="n">
-        <v>-12.6942</v>
+        <v>-4.1423</v>
       </c>
       <c r="U19" t="n">
-        <v>-4.1369</v>
+        <v>-1.9456</v>
       </c>
       <c r="V19" t="n">
         <v>-1.7268</v>
@@ -1969,13 +1969,13 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>-195.2848</v>
+        <v>-174.8424</v>
       </c>
       <c r="E20" t="n">
-        <v>-180.9778</v>
+        <v>-174.0176</v>
       </c>
       <c r="F20" t="n">
-        <v>-14.3067</v>
+        <v>-0.8248000000000006</v>
       </c>
       <c r="G20" t="n">
         <v>-139.1316</v>
@@ -1993,7 +1993,7 @@
         <v>114.2405</v>
       </c>
       <c r="L20" t="n">
-        <v>29.13049999999999</v>
+        <v>29.1305</v>
       </c>
       <c r="M20" t="n">
         <v>-282.5015</v>
@@ -2005,22 +2005,22 @@
         <v>-71.66079999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.953399999999998</v>
+        <v>-1.953399999999997</v>
       </c>
       <c r="Q20" t="n">
         <v>-440.4967</v>
       </c>
       <c r="R20" t="n">
-        <v>438.5439999999999</v>
+        <v>438.544</v>
       </c>
       <c r="S20" t="n">
-        <v>-33.538</v>
+        <v>-13.0959</v>
       </c>
       <c r="T20" t="n">
-        <v>-10.0912</v>
+        <v>-3.132099999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>-23.4461</v>
+        <v>-9.963300000000002</v>
       </c>
       <c r="V20" t="n">
         <v>-20.6621</v>
